--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J47-FunctionCode-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J47-FunctionCode-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240126120000</t>
+    <t>20241120120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-11-20T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R259-HL7ParticipationFunction/FHIR/TRE-R259-HL7ParticipationFunction</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Coordonnateur de parcours</t>
   </si>
   <si>
     <t>353</t>
@@ -583,7 +589,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -608,18 +614,26 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>52</v>
+      <c r="B5" t="s" s="2">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
